--- a/balance/Spiria_Game_spirit.xlsx
+++ b/balance/Spiria_Game_spirit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dawoonkim/Desktop/spiria game/balance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2809026B-8A4F-4946-9E75-DF86DF71E605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320988BB-A0FA-3E46-B92F-13DBA4B7C729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="27860" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -927,13 +927,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>고대 서고의 사서가 헐레벌떡 달려왔습니다.
-“책의 글자가 하나씩 사라지고 있어요!” 
-오래된 주문의 흔적과 공기처럼 흐르는 신비한 빛, 
-그리고 태양의 결정만이 기록을 붙잡고 있습니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>마법 → 태양 → 보석</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -949,6 +942,13 @@
 고대 유적 봉인에 균열 발생.  
 오래된 주문의 흔적과 형태 없이 흐르던 기운, 
 햇빛을 품은 결정의 광채도 사라지고 있음.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대 서고의 사서가 헐레벌떡 달려왔습니다.
+“책의 글자가 하나씩 사라지고 있어요!” 
+오래된 주문의 흔적과 신비한 기운, 
+그리고 태양의 결정만이 기록을 붙잡고 있습니다.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1310,13 +1310,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1792,10 +1792,10 @@
       <c r="T2" t="s">
         <v>206</v>
       </c>
-      <c r="U2" s="47" t="s">
+      <c r="U2" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="V2" s="47" t="s">
+      <c r="V2" s="45" t="s">
         <v>213</v>
       </c>
     </row>
@@ -1857,13 +1857,13 @@
       <c r="S3" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="47" t="s">
+      <c r="T3" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="U3" s="47" t="s">
+      <c r="U3" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="V3" s="47" t="s">
+      <c r="V3" s="45" t="s">
         <v>212</v>
       </c>
     </row>
@@ -1925,13 +1925,13 @@
       <c r="S4" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="T4" s="47" t="s">
+      <c r="T4" s="45" t="s">
         <v>208</v>
       </c>
       <c r="U4" t="s">
         <v>211</v>
       </c>
-      <c r="V4" s="47" t="s">
+      <c r="V4" s="45" t="s">
         <v>214</v>
       </c>
     </row>
@@ -1993,13 +1993,13 @@
       <c r="S5" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="T5" s="47" t="s">
+      <c r="T5" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="U5" s="47" t="s">
+      <c r="U5" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="V5" s="47" t="s">
+      <c r="V5" s="45" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2061,13 +2061,13 @@
       <c r="S6" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="T6" s="47" t="s">
+      <c r="T6" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="U6" s="47" t="s">
+      <c r="U6" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="V6" s="47" t="s">
+      <c r="V6" s="45" t="s">
         <v>216</v>
       </c>
     </row>
@@ -2129,10 +2129,10 @@
       <c r="S7" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="T7" s="47" t="s">
+      <c r="T7" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="U7" s="47" t="s">
+      <c r="U7" s="45" t="s">
         <v>199</v>
       </c>
       <c r="V7" t="s">
@@ -2197,13 +2197,13 @@
       <c r="S8" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="T8" s="47" t="s">
+      <c r="T8" s="45" t="s">
         <v>191</v>
       </c>
       <c r="U8" t="s">
         <v>200</v>
       </c>
-      <c r="V8" s="47" t="s">
+      <c r="V8" s="45" t="s">
         <v>219</v>
       </c>
     </row>
@@ -2265,13 +2265,13 @@
       <c r="S9" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="T9" s="47" t="s">
+      <c r="T9" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="U9" s="47" t="s">
+      <c r="U9" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="V9" s="47" t="s">
+      <c r="V9" s="45" t="s">
         <v>218</v>
       </c>
     </row>
@@ -2333,13 +2333,13 @@
       <c r="S10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="T10" s="47" t="s">
+      <c r="T10" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="U10" s="47" t="s">
+      <c r="U10" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="V10" s="47" t="s">
+      <c r="V10" s="45" t="s">
         <v>220</v>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>119</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J11" s="26" t="s">
         <v>120</v>
@@ -2401,13 +2401,13 @@
       <c r="S11" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="T11" s="47" t="s">
+      <c r="T11" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="U11" s="47" t="s">
+      <c r="U11" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="V11" s="47" t="s">
+      <c r="V11" s="45" t="s">
         <v>221</v>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         <v>128</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>129</v>
@@ -2469,13 +2469,13 @@
       <c r="S12" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="T12" s="47" t="s">
+      <c r="T12" s="45" t="s">
         <v>195</v>
       </c>
       <c r="U12" t="s">
         <v>204</v>
       </c>
-      <c r="V12" s="47" t="s">
+      <c r="V12" s="45" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13" s="34" t="s">
         <v>122</v>
@@ -2505,7 +2505,7 @@
         <v>137</v>
       </c>
       <c r="I13" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J13" s="33" t="s">
         <v>138</v>
@@ -2537,13 +2537,13 @@
       <c r="S13" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="T13" s="47" t="s">
+      <c r="T13" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="U13" s="47" t="s">
+      <c r="U13" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="V13" s="47" t="s">
+      <c r="V13" s="45" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">

--- a/balance/Spiria_Game_spirit.xlsx
+++ b/balance/Spiria_Game_spirit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dawoonkim/Desktop/spiria game/balance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320988BB-A0FA-3E46-B92F-13DBA4B7C729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92D94C6-03BF-DA49-B274-4815C35B1B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="27860" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,9 +356,6 @@
     <t>“네가 하고 싶었던 말, 내가 별빛에 실어 보내 줄까?”</t>
   </si>
   <si>
-    <t>“진심은 늦게 도착해도 결국 누군가의 마음에 닿아.”</t>
-  </si>
-  <si>
     <t>차가운 푸른빛</t>
   </si>
   <si>
@@ -722,10 +719,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"물결과 노래는 모두 떨림으로 멀리 마음을 전해."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>"같은 별을 바라봐도 
 빛이 닿는 각도에 따라 다르게 보인대."</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -741,19 +734,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"물결은 지나가도 그 움직임은 다른 물결로 계속 이어져."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>"단단한 돌에도 작은 틈은 있지만, 
 그 틈이 빛이 들어오는 길이 되기도 해."</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"지금 보는 별빛은 아주 오래전 별이 떠나보낸 빛이래."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>"잎맥은 물과 양분이 오가는 길이야. 
 작은 잎 안에도 수많은 길이 있지."</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -774,10 +759,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"뿌리는 빛이 없는 곳에서도 물이 있는 방향을 찾아 자라."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>"나무는 움직이지 않아도 
 빛과 바람을 따라 매일 조금씩 달라져."</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -803,10 +784,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"불은 가진 온기를 주변으로 나누면서 빛을 만들어."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>"빛은 사라진 게 아니라, 
 때로는 우리가 보지 못하는 방향으로 향하고 있어."</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -838,12 +815,6 @@
   </si>
   <si>
     <t>별 → 꽃 → 마법</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>밤하늘의 별빛이 점점 사라지고 있습니다. 
-꽃잎에 깃든 신비로운 기운이 빛을 붙잡고 있는 걸까요, 
-아니면 달빛 비친 호수에 별빛이 스며든 걸까요?</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -949,6 +920,42 @@
 “책의 글자가 하나씩 사라지고 있어요!” 
 오래된 주문의 흔적과 신비한 기운, 
 그리고 태양의 결정만이 기록을 붙잡고 있습니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"물결은 지나가도 
+그 움직임은 다른 물결로 계속 이어져."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"불은 가진 온기를 
+주변으로 나누면서 빛을 만들어."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"물결과 노래는 
+모두 떨림으로 멀리 마음을 전해."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>“진심은 늦게 도착해도 결국 누군가의 마음에 닿아.”</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"뿌리는 빛이 없는 곳에서도 
+물이 있는 방향을 찾아 자라."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"지금 보는 별빛은 
+아주 오래전 별이 떠나보낸 빛이래."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤하늘의 별빛이 점점 사라지고 있습니다. 
+꽃잎에 깃든 신비로운 기운이 
+빛을 붙잡고 있는 걸까요, 
+아니면 달빛 비친 호수에 별빛이 스며든 걸까요?</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1660,7 +1667,8 @@
     <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="46" customWidth="1"/>
     <col min="17" max="19" width="39.5" customWidth="1"/>
-    <col min="20" max="22" width="33.83203125" customWidth="1"/>
+    <col min="20" max="21" width="33.83203125" customWidth="1"/>
+    <col min="22" max="22" width="50.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="33.75" customHeight="1">
@@ -1736,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>22</v>
@@ -1757,7 +1765,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>28</v>
@@ -1772,7 +1780,7 @@
         <v>94</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="O2" s="21">
         <v>74</v>
@@ -1789,14 +1797,14 @@
       <c r="S2" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="T2" t="s">
-        <v>206</v>
+      <c r="T2" s="45" t="s">
+        <v>243</v>
       </c>
       <c r="U2" s="45" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="V2" s="45" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="91.5" customHeight="1">
@@ -1804,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>35</v>
@@ -1825,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J3" s="26" t="s">
         <v>39</v>
@@ -1858,13 +1866,13 @@
         <v>45</v>
       </c>
       <c r="T3" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="U3" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="V3" s="45" t="s">
         <v>207</v>
-      </c>
-      <c r="U3" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="V3" s="45" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="91.5" customHeight="1">
@@ -1872,7 +1880,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>46</v>
@@ -1893,7 +1901,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>50</v>
@@ -1926,13 +1934,13 @@
         <v>56</v>
       </c>
       <c r="T4" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="U4" t="s">
-        <v>211</v>
+        <v>204</v>
+      </c>
+      <c r="U4" s="45" t="s">
+        <v>242</v>
       </c>
       <c r="V4" s="45" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="91.5" customHeight="1">
@@ -1961,7 +1969,7 @@
         <v>62</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="J5" s="26" t="s">
         <v>63</v>
@@ -1988,19 +1996,19 @@
         <v>67</v>
       </c>
       <c r="R5" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S5" s="43" t="s">
         <v>68</v>
       </c>
       <c r="T5" s="45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V5" s="45" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="91.5" customHeight="1">
@@ -2029,7 +2037,7 @@
         <v>27</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="J6" s="26" t="s">
         <v>71</v>
@@ -2062,13 +2070,13 @@
         <v>75</v>
       </c>
       <c r="T6" s="45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U6" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V6" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="91.5" customHeight="1">
@@ -2097,7 +2105,7 @@
         <v>81</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>82</v>
@@ -2130,13 +2138,13 @@
         <v>87</v>
       </c>
       <c r="T7" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U7" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="V7" t="s">
-        <v>217</v>
+        <v>198</v>
+      </c>
+      <c r="V7" s="45" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="91.5" customHeight="1">
@@ -2144,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>88</v>
@@ -2165,7 +2173,7 @@
         <v>91</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="J8" s="26" t="s">
         <v>92</v>
@@ -2195,16 +2203,16 @@
         <v>96</v>
       </c>
       <c r="S8" s="44" t="s">
-        <v>97</v>
+        <v>241</v>
       </c>
       <c r="T8" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="U8" t="s">
-        <v>200</v>
+        <v>190</v>
+      </c>
+      <c r="U8" s="45" t="s">
+        <v>240</v>
       </c>
       <c r="V8" s="45" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="91.5" customHeight="1">
@@ -2212,13 +2220,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>89</v>
@@ -2227,19 +2235,19 @@
         <v>47</v>
       </c>
       <c r="G9" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="I9" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="J9" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" s="26" t="s">
+      <c r="K9" s="26" t="s">
         <v>101</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>102</v>
       </c>
       <c r="L9" s="27" t="s">
         <v>30</v>
@@ -2254,25 +2262,25 @@
         <v>73</v>
       </c>
       <c r="P9" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="Q9" s="43" t="s">
+      <c r="R9" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="R9" s="43" t="s">
+      <c r="S9" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="S9" s="44" t="s">
-        <v>106</v>
-      </c>
       <c r="T9" s="45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U9" s="45" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="V9" s="45" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="91.5" customHeight="1">
@@ -2280,7 +2288,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>52</v>
@@ -2295,19 +2303,19 @@
         <v>79</v>
       </c>
       <c r="G10" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="I10" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="J10" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" s="33" t="s">
+      <c r="K10" s="33" t="s">
         <v>109</v>
-      </c>
-      <c r="K10" s="33" t="s">
-        <v>110</v>
       </c>
       <c r="L10" s="37" t="s">
         <v>52</v>
@@ -2322,25 +2330,25 @@
         <v>76</v>
       </c>
       <c r="P10" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="S10" s="44" t="s">
-        <v>114</v>
-      </c>
       <c r="T10" s="45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U10" s="45" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="V10" s="45" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="91.5" customHeight="1">
@@ -2348,67 +2356,67 @@
         <v>10</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>115</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>116</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>59</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="I11" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="J11" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I11" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="J11" s="26" t="s">
+      <c r="K11" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="K11" s="26" t="s">
-        <v>121</v>
-      </c>
       <c r="L11" s="27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M11" s="28">
         <v>94</v>
       </c>
       <c r="N11" s="29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O11" s="30">
         <v>71</v>
       </c>
       <c r="P11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q11" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="Q11" s="43" t="s">
+      <c r="R11" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="R11" s="44" t="s">
+      <c r="S11" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="S11" s="43" t="s">
-        <v>126</v>
-      </c>
       <c r="T11" s="45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U11" s="45" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="V11" s="45" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="91.5" customHeight="1">
@@ -2416,34 +2424,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="I12" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="J12" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="J12" s="26" t="s">
+      <c r="K12" s="26" t="s">
         <v>129</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>130</v>
       </c>
       <c r="L12" s="27" t="s">
         <v>65</v>
@@ -2458,25 +2466,25 @@
         <v>72</v>
       </c>
       <c r="P12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q12" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="Q12" s="43" t="s">
+      <c r="R12" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="R12" s="43" t="s">
+      <c r="S12" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="S12" s="43" t="s">
-        <v>134</v>
-      </c>
       <c r="T12" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="U12" t="s">
-        <v>204</v>
+        <v>194</v>
+      </c>
+      <c r="U12" s="45" t="s">
+        <v>238</v>
       </c>
       <c r="V12" s="45" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="91.5" customHeight="1">
@@ -2484,67 +2492,67 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F13" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="H13" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="33" t="s">
+      <c r="I13" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="J13" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="J13" s="33" t="s">
+      <c r="K13" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="K13" s="33" t="s">
-        <v>139</v>
-      </c>
       <c r="L13" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M13" s="38">
         <v>98</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O13" s="39">
         <v>69</v>
       </c>
       <c r="P13" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q13" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="Q13" s="43" t="s">
+      <c r="R13" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="R13" s="43" t="s">
+      <c r="S13" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="S13" s="43" t="s">
-        <v>143</v>
-      </c>
       <c r="T13" s="45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U13" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="V13" s="45" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2585,7 +2593,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1">
       <c r="A1" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2593,170 +2601,170 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="C4" s="5">
         <v>30</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="5">
         <v>15</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="5">
         <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5">
         <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="C8" s="5">
         <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="5">
         <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" customHeight="1">
@@ -2767,24 +2775,24 @@
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>180</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1">
       <c r="A17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>60</v>
@@ -2795,10 +2803,10 @@
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>89</v>
@@ -2809,10 +2817,10 @@
     </row>
     <row r="19" spans="1:4" ht="36" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="13"/>

--- a/balance/Spiria_Game_spirit.xlsx
+++ b/balance/Spiria_Game_spirit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dawoonkim/Desktop/spiria game/balance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92D94C6-03BF-DA49-B274-4815C35B1B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCB2F32-2126-0E42-95B3-F65192996B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="27860" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34200" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정령·의뢰서 합본" sheetId="1" r:id="rId1"/>
@@ -210,9 +210,6 @@
     <t>“오늘은 네 마음에 어떤 꽃을 피워 볼까?”</t>
   </si>
   <si>
-    <t xml:space="preserve">물 → 달 → 별 </t>
-  </si>
-  <si>
     <t>플레오</t>
   </si>
   <si>
@@ -956,6 +953,10 @@
 꽃잎에 깃든 신비로운 기운이 
 빛을 붙잡고 있는 걸까요, 
 아니면 달빛 비친 호수에 별빛이 스며든 걸까요?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">달 → 별 → 에테르 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1744,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>22</v>
@@ -1765,7 +1766,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>28</v>
@@ -1780,7 +1781,7 @@
         <v>94</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O2" s="21">
         <v>74</v>
@@ -1798,13 +1799,13 @@
         <v>34</v>
       </c>
       <c r="T2" s="45" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U2" s="45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V2" s="45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="91.5" customHeight="1">
@@ -1812,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>35</v>
@@ -1833,7 +1834,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J3" s="26" t="s">
         <v>39</v>
@@ -1866,13 +1867,13 @@
         <v>45</v>
       </c>
       <c r="T3" s="45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U3" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="V3" s="45" t="s">
         <v>206</v>
-      </c>
-      <c r="V3" s="45" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="91.5" customHeight="1">
@@ -1880,7 +1881,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>46</v>
@@ -1901,7 +1902,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>50</v>
@@ -1934,13 +1935,13 @@
         <v>56</v>
       </c>
       <c r="T4" s="45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U4" s="45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V4" s="45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="91.5" customHeight="1">
@@ -1948,67 +1949,67 @@
         <v>4</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="D5" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>59</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>60</v>
       </c>
       <c r="F5" s="24" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="I5" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J5" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="J5" s="26" t="s">
+      <c r="K5" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="26" t="s">
-        <v>64</v>
-      </c>
       <c r="L5" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M5" s="28">
         <v>94</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O5" s="30">
         <v>73</v>
       </c>
       <c r="P5" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="Q5" s="43" t="s">
+      <c r="R5" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="S5" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="R5" s="44" t="s">
+      <c r="T5" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="S5" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="T5" s="45" t="s">
-        <v>187</v>
-      </c>
       <c r="U5" s="45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V5" s="45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="91.5" customHeight="1">
@@ -2016,7 +2017,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>41</v>
@@ -2025,22 +2026,22 @@
         <v>23</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="24" t="s">
         <v>47</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>29</v>
@@ -2058,25 +2059,25 @@
         <v>74</v>
       </c>
       <c r="P6" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="Q6" s="44" t="s">
+      <c r="R6" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="R6" s="43" t="s">
+      <c r="S6" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="S6" s="43" t="s">
-        <v>75</v>
-      </c>
       <c r="T6" s="45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U6" s="45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V6" s="45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="91.5" customHeight="1">
@@ -2084,37 +2085,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="D7" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="E7" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="36" t="s">
+      <c r="G7" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="H7" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="I7" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="J7" s="33" t="s">
+      <c r="K7" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="K7" s="33" t="s">
-        <v>83</v>
-      </c>
       <c r="L7" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M7" s="38">
         <v>96</v>
@@ -2126,25 +2127,25 @@
         <v>75</v>
       </c>
       <c r="P7" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="Q7" s="44" t="s">
+      <c r="R7" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="R7" s="43" t="s">
+      <c r="S7" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="S7" s="44" t="s">
-        <v>87</v>
-      </c>
       <c r="T7" s="45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U7" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V7" s="45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="91.5" customHeight="1">
@@ -2152,37 +2153,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>89</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="I8" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="J8" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="J8" s="26" t="s">
+      <c r="K8" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>93</v>
-      </c>
       <c r="L8" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M8" s="28">
         <v>95</v>
@@ -2194,25 +2195,25 @@
         <v>74</v>
       </c>
       <c r="P8" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="Q8" s="43" t="s">
+      <c r="R8" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="R8" s="44" t="s">
-        <v>96</v>
-      </c>
       <c r="S8" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T8" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U8" s="45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V8" s="45" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="91.5" customHeight="1">
@@ -2220,34 +2221,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="I9" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="J9" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="26" t="s">
+      <c r="K9" s="26" t="s">
         <v>100</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>101</v>
       </c>
       <c r="L9" s="27" t="s">
         <v>30</v>
@@ -2262,25 +2263,25 @@
         <v>73</v>
       </c>
       <c r="P9" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q9" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="Q9" s="43" t="s">
+      <c r="R9" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="R9" s="43" t="s">
+      <c r="S9" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="S9" s="44" t="s">
-        <v>105</v>
-      </c>
       <c r="T9" s="45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U9" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="V9" s="45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="91.5" customHeight="1">
@@ -2288,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>52</v>
@@ -2297,25 +2298,25 @@
         <v>23</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="I10" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="J10" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="J10" s="33" t="s">
+      <c r="K10" s="33" t="s">
         <v>108</v>
-      </c>
-      <c r="K10" s="33" t="s">
-        <v>109</v>
       </c>
       <c r="L10" s="37" t="s">
         <v>52</v>
@@ -2324,31 +2325,31 @@
         <v>94</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O10" s="39">
         <v>76</v>
       </c>
       <c r="P10" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="S10" s="44" t="s">
-        <v>113</v>
-      </c>
       <c r="T10" s="45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U10" s="45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V10" s="45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="91.5" customHeight="1">
@@ -2356,67 +2357,67 @@
         <v>10</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="D11" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>115</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>116</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="I11" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="I11" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="J11" s="26" t="s">
+      <c r="K11" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="K11" s="26" t="s">
-        <v>120</v>
-      </c>
       <c r="L11" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M11" s="28">
         <v>94</v>
       </c>
       <c r="N11" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O11" s="30">
         <v>71</v>
       </c>
       <c r="P11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="Q11" s="43" t="s">
+      <c r="R11" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="R11" s="44" t="s">
+      <c r="S11" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="S11" s="43" t="s">
-        <v>125</v>
-      </c>
       <c r="T11" s="45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U11" s="45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="V11" s="45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="91.5" customHeight="1">
@@ -2424,67 +2425,67 @@
         <v>11</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="I12" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="J12" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="I12" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="J12" s="26" t="s">
+      <c r="K12" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>129</v>
-      </c>
       <c r="L12" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M12" s="28">
         <v>95</v>
       </c>
       <c r="N12" s="29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O12" s="30">
         <v>72</v>
       </c>
       <c r="P12" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q12" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="Q12" s="43" t="s">
+      <c r="R12" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="R12" s="43" t="s">
+      <c r="S12" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="S12" s="43" t="s">
-        <v>133</v>
-      </c>
       <c r="T12" s="45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U12" s="45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V12" s="45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="91.5" customHeight="1">
@@ -2492,67 +2493,67 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F13" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="H13" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="H13" s="33" t="s">
+      <c r="I13" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="J13" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="I13" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="J13" s="33" t="s">
+      <c r="K13" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="K13" s="33" t="s">
-        <v>138</v>
-      </c>
       <c r="L13" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M13" s="38">
         <v>98</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O13" s="39">
         <v>69</v>
       </c>
       <c r="P13" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q13" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="Q13" s="43" t="s">
+      <c r="R13" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="R13" s="43" t="s">
+      <c r="S13" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="S13" s="43" t="s">
-        <v>142</v>
-      </c>
       <c r="T13" s="45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U13" s="45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="V13" s="45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2593,7 +2594,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1">
       <c r="A1" s="46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2601,170 +2602,170 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="C4" s="5">
         <v>30</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="5">
         <v>15</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C6" s="5">
         <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="5">
         <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="C8" s="5">
         <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" s="5">
         <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" customHeight="1">
@@ -2775,52 +2776,52 @@
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1">
       <c r="A17" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="C17" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>184</v>
-      </c>
       <c r="C18" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="36" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="13"/>
